--- a/exercise/Admin/Admin Distribusi/Tes Excel Admin Distribusi.xlsx
+++ b/exercise/Admin/Admin Distribusi/Tes Excel Admin Distribusi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\1. For Youtube\File Have Finished Youtube\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Distribusi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F99434F-FAAF-4E69-B203-A7080ADF4CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BE23BD-FE24-4089-B553-E757FE381968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="11070" xr2:uid="{46D4BEFD-E2CD-45F8-B6B5-13C2052FED5E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{46D4BEFD-E2CD-45F8-B6B5-13C2052FED5E}"/>
   </bookViews>
   <sheets>
     <sheet name="latihan" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="TABEL_WILAYAH">#REF!</definedName>
     <definedName name="TB">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +29,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -494,7 +496,7 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -540,10 +542,6 @@
     <xf numFmtId="42" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -558,32 +556,32 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="41" fontId="5" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -934,10 +932,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="32"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -952,54 +950,54 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="33" t="s">
+      <c r="I2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="35" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="1"/>
-      <c r="L2" s="36" t="s">
+      <c r="L2" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="37"/>
+      <c r="M2" s="38"/>
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="34"/>
+      <c r="A3" s="31"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="35"/>
       <c r="K3" s="1"/>
       <c r="L3" s="7" t="s">
         <v>7</v>
@@ -1010,24 +1008,42 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="23">
         <v>1</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="24">
         <v>44206</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="29">
+      <c r="D4" s="23" t="str">
+        <f>_xlfn.XLOOKUP(LEFT(C4,2),$L$4:$L$8,$M$4:$M$8)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="E4" s="23" t="str">
+        <f>_xlfn.XLOOKUP(MID(C4,3,2),$O$7:$O$11,$P$7:$P$11)</f>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F4" s="23" t="str">
+        <f>_xlfn.XLOOKUP(RIGHT(C4,3),$L$12:$L$16,$M$12:$M$16)</f>
+        <v>Bandung</v>
+      </c>
+      <c r="G4" s="26">
+        <f>_xlfn.XLOOKUP(E4,$P$7:$P$11,$Q$7:$Q$11)</f>
+        <v>1500000</v>
+      </c>
+      <c r="H4" s="27">
         <v>56</v>
       </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="28">
+        <f>IF(H4&gt;50,10%,0)</f>
+        <v>0.1</v>
+      </c>
+      <c r="J4" s="26">
+        <f>(G4*H4)-(G4*H4*I4)</f>
+        <v>75600000</v>
+      </c>
       <c r="K4" s="1"/>
       <c r="L4" s="11" t="s">
         <v>13</v>
@@ -1041,24 +1057,42 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="25">
+      <c r="A5" s="23">
         <v>2</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="24">
         <v>44207</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29">
+      <c r="D5" s="23" t="str">
+        <f t="shared" ref="D5:D18" si="0">_xlfn.XLOOKUP(LEFT(C5,2),$L$4:$L$8,$M$4:$M$8)</f>
+        <v>Kevin</v>
+      </c>
+      <c r="E5" s="23" t="str">
+        <f t="shared" ref="E5:E18" si="1">_xlfn.XLOOKUP(MID(C5,3,2),$O$7:$O$11,$P$7:$P$11)</f>
+        <v>OPPO A53</v>
+      </c>
+      <c r="F5" s="23" t="str">
+        <f t="shared" ref="F5:F18" si="2">_xlfn.XLOOKUP(RIGHT(C5,3),$L$12:$L$16,$M$12:$M$16)</f>
+        <v>Jakarta</v>
+      </c>
+      <c r="G5" s="26">
+        <f t="shared" ref="G5:G18" si="3">_xlfn.XLOOKUP(E5,$P$7:$P$11,$Q$7:$Q$11)</f>
+        <v>2000000</v>
+      </c>
+      <c r="H5" s="27">
         <v>23</v>
       </c>
-      <c r="I5" s="30"/>
-      <c r="J5" s="28"/>
+      <c r="I5" s="28">
+        <f t="shared" ref="I5:I18" si="4">IF(H5&gt;50,10%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="26">
+        <f t="shared" ref="J5:J18" si="5">(G5*H5)-(G5*H5*I5)</f>
+        <v>46000000</v>
+      </c>
       <c r="K5" s="1"/>
       <c r="L5" s="12" t="s">
         <v>14</v>
@@ -1067,31 +1101,49 @@
         <v>24</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="36" t="s">
+      <c r="O5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
     </row>
     <row r="6" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="25">
+      <c r="A6" s="23">
         <v>3</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="24">
         <v>44208</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29">
+      <c r="D6" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Luna Maya</v>
+      </c>
+      <c r="E6" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A59</v>
+      </c>
+      <c r="F6" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Semarang</v>
+      </c>
+      <c r="G6" s="26">
+        <f t="shared" si="3"/>
+        <v>2500000</v>
+      </c>
+      <c r="H6" s="27">
         <v>85</v>
       </c>
-      <c r="I6" s="30"/>
-      <c r="J6" s="28"/>
+      <c r="I6" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J6" s="26">
+        <f t="shared" si="5"/>
+        <v>191250000</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="12" t="s">
         <v>15</v>
@@ -1111,24 +1163,42 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
+      <c r="A7" s="23">
         <v>4</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="24">
         <v>44209</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29">
+      <c r="D7" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Fitri Lestari</v>
+      </c>
+      <c r="E7" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F7" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Bandung</v>
+      </c>
+      <c r="G7" s="26">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="H7" s="27">
         <v>56</v>
       </c>
-      <c r="I7" s="30"/>
-      <c r="J7" s="28"/>
+      <c r="I7" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J7" s="26">
+        <f t="shared" si="5"/>
+        <v>75600000</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="12" t="s">
         <v>16</v>
@@ -1148,24 +1218,42 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25">
+      <c r="A8" s="23">
         <v>5</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="24">
         <v>44210</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29">
+      <c r="D8" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Cristin</v>
+      </c>
+      <c r="E8" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F8" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Semarang</v>
+      </c>
+      <c r="G8" s="26">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="H8" s="27">
         <v>62</v>
       </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="28"/>
+      <c r="I8" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="26">
+        <f t="shared" si="5"/>
+        <v>83700000</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="13" t="s">
         <v>17</v>
@@ -1185,27 +1273,45 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
+      <c r="A9" s="23">
         <v>6</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="24">
         <v>44211</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29">
+      <c r="D9" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Angga Wira</v>
+      </c>
+      <c r="E9" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO F9</v>
+      </c>
+      <c r="F9" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Bandung</v>
+      </c>
+      <c r="G9" s="26">
+        <f t="shared" si="3"/>
+        <v>10000000</v>
+      </c>
+      <c r="H9" s="27">
         <v>23</v>
       </c>
-      <c r="I9" s="30"/>
-      <c r="J9" s="28"/>
+      <c r="I9" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J9" s="26">
+        <f t="shared" si="5"/>
+        <v>230000000</v>
+      </c>
       <c r="K9" s="1"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="24"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="12" t="s">
         <v>43</v>
@@ -1218,29 +1324,47 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25">
+      <c r="A10" s="23">
         <v>7</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="24">
         <v>44212</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29">
+      <c r="D10" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Cristin</v>
+      </c>
+      <c r="E10" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A59</v>
+      </c>
+      <c r="F10" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Semarang</v>
+      </c>
+      <c r="G10" s="26">
+        <f t="shared" si="3"/>
+        <v>2500000</v>
+      </c>
+      <c r="H10" s="27">
         <v>60</v>
       </c>
-      <c r="I10" s="30"/>
-      <c r="J10" s="28"/>
+      <c r="I10" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J10" s="26">
+        <f t="shared" si="5"/>
+        <v>135000000</v>
+      </c>
       <c r="K10" s="1"/>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="M10" s="37"/>
+      <c r="M10" s="38"/>
       <c r="N10" s="1"/>
       <c r="O10" s="12" t="s">
         <v>44</v>
@@ -1253,24 +1377,42 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="25">
+      <c r="A11" s="23">
         <v>8</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="24">
         <v>44213</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29">
+      <c r="D11" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Kevin</v>
+      </c>
+      <c r="E11" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO F9</v>
+      </c>
+      <c r="F11" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Jakarta</v>
+      </c>
+      <c r="G11" s="26">
+        <f t="shared" si="3"/>
+        <v>10000000</v>
+      </c>
+      <c r="H11" s="27">
         <v>35</v>
       </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="28"/>
+      <c r="I11" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="26">
+        <f t="shared" si="5"/>
+        <v>350000000</v>
+      </c>
       <c r="K11" s="1"/>
       <c r="L11" s="21" t="s">
         <v>7</v>
@@ -1290,24 +1432,42 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
+      <c r="A12" s="23">
         <v>9</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="24">
         <v>44214</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29">
+      <c r="D12" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Angga Wira</v>
+      </c>
+      <c r="E12" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F12" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Jakarta</v>
+      </c>
+      <c r="G12" s="26">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="H12" s="27">
         <v>66</v>
       </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="28"/>
+      <c r="I12" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="26">
+        <f t="shared" si="5"/>
+        <v>89100000</v>
+      </c>
       <c r="K12" s="1"/>
       <c r="L12" s="11" t="s">
         <v>34</v>
@@ -1321,24 +1481,42 @@
       <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="A13" s="23">
         <v>10</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="24">
         <v>44215</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29">
+      <c r="D13" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Fitri Lestari</v>
+      </c>
+      <c r="E13" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO F9</v>
+      </c>
+      <c r="F13" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Yogyakarta</v>
+      </c>
+      <c r="G13" s="26">
+        <f t="shared" si="3"/>
+        <v>10000000</v>
+      </c>
+      <c r="H13" s="27">
         <v>47</v>
       </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="28"/>
+      <c r="I13" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="26">
+        <f t="shared" si="5"/>
+        <v>470000000</v>
+      </c>
       <c r="K13" s="1"/>
       <c r="L13" s="12" t="s">
         <v>35</v>
@@ -1347,31 +1525,49 @@
         <v>30</v>
       </c>
       <c r="N13" s="1"/>
-      <c r="O13" s="35" t="s">
+      <c r="O13" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
     </row>
     <row r="14" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
+      <c r="A14" s="23">
         <v>11</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="24">
         <v>44216</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29">
+      <c r="D14" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Kevin</v>
+      </c>
+      <c r="E14" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F14" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Bandung</v>
+      </c>
+      <c r="G14" s="26">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="H14" s="27">
         <v>81</v>
       </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="28"/>
+      <c r="I14" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="26">
+        <f t="shared" si="5"/>
+        <v>109350000</v>
+      </c>
       <c r="K14" s="1"/>
       <c r="L14" s="12" t="s">
         <v>36</v>
@@ -1380,31 +1576,49 @@
         <v>31</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" s="31" t="s">
+      <c r="O14" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="31"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
     </row>
     <row r="15" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+      <c r="A15" s="23">
         <v>12</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="24">
         <v>44217</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29">
+      <c r="D15" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Luna Maya</v>
+      </c>
+      <c r="E15" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A59</v>
+      </c>
+      <c r="F15" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Yogyakarta</v>
+      </c>
+      <c r="G15" s="26">
+        <f t="shared" si="3"/>
+        <v>2500000</v>
+      </c>
+      <c r="H15" s="27">
         <v>59</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="28"/>
+      <c r="I15" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J15" s="26">
+        <f t="shared" si="5"/>
+        <v>132750000</v>
+      </c>
       <c r="K15" s="1"/>
       <c r="L15" s="12" t="s">
         <v>37</v>
@@ -1413,31 +1627,49 @@
         <v>32</v>
       </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="32" t="s">
+      <c r="O15" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
     </row>
     <row r="16" spans="1:17" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="25">
+      <c r="A16" s="23">
         <v>13</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="24">
         <v>44218</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29">
+      <c r="D16" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Cristin</v>
+      </c>
+      <c r="E16" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO F9</v>
+      </c>
+      <c r="F16" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Bandung</v>
+      </c>
+      <c r="G16" s="26">
+        <f t="shared" si="3"/>
+        <v>10000000</v>
+      </c>
+      <c r="H16" s="27">
         <v>25</v>
       </c>
-      <c r="I16" s="30"/>
-      <c r="J16" s="28"/>
+      <c r="I16" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="26">
+        <f t="shared" si="5"/>
+        <v>250000000</v>
+      </c>
       <c r="K16" s="1"/>
       <c r="L16" s="13" t="s">
         <v>38</v>
@@ -1451,24 +1683,42 @@
       <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+      <c r="A17" s="23">
         <v>14</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="24">
         <v>44219</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29">
+      <c r="D17" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Luna Maya</v>
+      </c>
+      <c r="E17" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A53</v>
+      </c>
+      <c r="F17" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Jakarta</v>
+      </c>
+      <c r="G17" s="26">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
+      <c r="H17" s="27">
         <v>64</v>
       </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="28"/>
+      <c r="I17" s="28">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="J17" s="26">
+        <f t="shared" si="5"/>
+        <v>115200000</v>
+      </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -1478,24 +1728,42 @@
       <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+      <c r="A18" s="23">
         <v>15</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="24">
         <v>44220</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29">
+      <c r="D18" s="23" t="str">
+        <f t="shared" si="0"/>
+        <v>Fitri Lestari</v>
+      </c>
+      <c r="E18" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>OPPO A37</v>
+      </c>
+      <c r="F18" s="23" t="str">
+        <f t="shared" si="2"/>
+        <v>Yogyakarta</v>
+      </c>
+      <c r="G18" s="26">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="H18" s="27">
         <v>44</v>
       </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="28"/>
+      <c r="I18" s="28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="26">
+        <f t="shared" si="5"/>
+        <v>66000000</v>
+      </c>
       <c r="K18" s="1"/>
       <c r="L18" s="19"/>
       <c r="M18" s="18"/>
@@ -1515,14 +1783,14 @@
       <c r="C20" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="E20" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="39"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
       <c r="O20" s="18"/>
       <c r="P20" s="18"/>
       <c r="Q20" s="18"/>
@@ -1534,13 +1802,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
     <mergeCell ref="O14:Q14"/>
     <mergeCell ref="O15:Q15"/>
     <mergeCell ref="F2:F3"/>
@@ -1552,6 +1813,13 @@
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="O5:Q5"/>
     <mergeCell ref="L10:M10"/>
+    <mergeCell ref="E20:J20"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E20" r:id="rId1" xr:uid="{38EC8BA4-0A36-4649-8782-28F881C9CBC9}"/>
